--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484341_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484341_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2361</v>
+        <v>4.9933</v>
       </c>
       <c r="E2" t="n">
-        <v>4.9517</v>
+        <v>4.7089</v>
       </c>
       <c r="F2" t="n">
         <v>0.2844</v>
@@ -610,10 +610,10 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2283</v>
+        <v>-0.0145</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3798</v>
+        <v>0.137</v>
       </c>
       <c r="U2" t="n">
         <v>-0.1515</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.331</v>
+        <v>4.3679</v>
       </c>
       <c r="E3" t="n">
-        <v>3.5585</v>
+        <v>4.0235</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2276</v>
+        <v>0.3444</v>
       </c>
       <c r="G3" t="n">
         <v>2.8641</v>
@@ -688,13 +688,13 @@
         <v>1.9534</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.6932</v>
+        <v>-0.6563</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.7784</v>
+        <v>-0.3135</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9147</v>
+        <v>-0.3428</v>
       </c>
       <c r="V3" t="n">
         <v>2.16</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.1882</v>
+        <v>1.8236</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2835</v>
+        <v>1.1104</v>
       </c>
       <c r="F4" t="n">
-        <v>1.9047</v>
+        <v>0.7131999999999999</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2739</v>
+        <v>-1.0959</v>
       </c>
       <c r="H4" t="n">
-        <v>0.8294</v>
+        <v>-0.0302</v>
       </c>
       <c r="I4" t="n">
-        <v>0.4445</v>
+        <v>-1.0657</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7593</v>
+        <v>0.1379</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7188</v>
+        <v>0.7982</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0405</v>
+        <v>-0.6603</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5145999999999999</v>
+        <v>-1.2338</v>
       </c>
       <c r="N4" t="n">
-        <v>0.1105</v>
+        <v>-0.8283</v>
       </c>
       <c r="O4" t="n">
-        <v>0.4041</v>
+        <v>-0.4054</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.3907</v>
+        <v>0.586</v>
       </c>
       <c r="Q4" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R4" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S4" t="n">
-        <v>1.2501</v>
+        <v>0.5056</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5009</v>
+        <v>0.4534</v>
       </c>
       <c r="U4" t="n">
-        <v>0.7492</v>
+        <v>0.0522</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0549</v>
+        <v>1.8279</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.4959</v>
       </c>
       <c r="X4" t="n">
-        <v>0.0549</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>A. SAMAKE EL ALAOUI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.7031</v>
+        <v>1.746</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5362</v>
+        <v>-0.1957</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1669</v>
+        <v>1.9417</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0617</v>
+        <v>2.2116</v>
       </c>
       <c r="H5" t="n">
-        <v>2.4257</v>
+        <v>4.2748</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.364</v>
+        <v>-2.0632</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9832</v>
+        <v>1.9865</v>
       </c>
       <c r="K5" t="n">
-        <v>1.6168</v>
+        <v>4.5881</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-2.6016</v>
       </c>
       <c r="M5" t="n">
-        <v>1.0786</v>
+        <v>0.2252</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8089</v>
+        <v>-0.3133</v>
       </c>
       <c r="O5" t="n">
-        <v>0.2696</v>
+        <v>0.5385</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q5" t="n">
+        <v>-2.9301</v>
+      </c>
+      <c r="R5" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.4025</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-0.3609</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-0.0415</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1.1089</v>
+      </c>
+      <c r="W5" t="n">
+        <v>1.1089</v>
+      </c>
+      <c r="X5" t="n">
         <v>0</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0.1953</v>
-      </c>
-      <c r="S5" t="n">
-        <v>0.6647</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0.5531</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.1117</v>
-      </c>
-      <c r="V5" t="n">
-        <v>-1.2186</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>-1.2186</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0397</v>
+        <v>1.427</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5443</v>
+        <v>1.2329</v>
       </c>
       <c r="F6" t="n">
-        <v>0.4953</v>
+        <v>0.1942</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.0959</v>
+        <v>2.0617</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0302</v>
+        <v>2.4257</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0657</v>
+        <v>-0.364</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1379</v>
+        <v>0.9832</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7982</v>
+        <v>1.6168</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6603</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.2338</v>
+        <v>1.0786</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8283</v>
+        <v>0.8089</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.4054</v>
+        <v>0.2696</v>
       </c>
       <c r="P6" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2784</v>
+        <v>0.3886</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1127</v>
+        <v>0.2497</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1657</v>
+        <v>0.1389</v>
       </c>
       <c r="V6" t="n">
-        <v>1.8279</v>
+        <v>-1.2186</v>
       </c>
       <c r="W6" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3321</v>
+        <v>-1.2186</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. SAMAKE EL ALAOUI</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6121</v>
+        <v>1.1051</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.1662</v>
+        <v>-0.3638</v>
       </c>
       <c r="F7" t="n">
-        <v>1.7783</v>
+        <v>1.469</v>
       </c>
       <c r="G7" t="n">
-        <v>2.2116</v>
+        <v>1.2739</v>
       </c>
       <c r="H7" t="n">
-        <v>4.2748</v>
+        <v>0.8294</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.0632</v>
+        <v>0.4445</v>
       </c>
       <c r="J7" t="n">
-        <v>1.9865</v>
+        <v>0.7593</v>
       </c>
       <c r="K7" t="n">
-        <v>4.5881</v>
+        <v>0.7188</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.6016</v>
+        <v>0.0405</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2252</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3133</v>
+        <v>0.1105</v>
       </c>
       <c r="O7" t="n">
-        <v>0.5385</v>
+        <v>0.4041</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1721</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R7" t="n">
-        <v>1.7581</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.5364</v>
+        <v>0.1671</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.3315</v>
+        <v>-0.1464</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2049</v>
+        <v>0.3135</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1089</v>
+        <v>0.0549</v>
       </c>
       <c r="W7" t="n">
-        <v>1.1089</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>0.0549</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4947</v>
+        <v>-0.0366</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.4387</v>
+        <v>-0.7765</v>
       </c>
       <c r="F8" t="n">
-        <v>1.944</v>
+        <v>0.74</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8814</v>
+        <v>-1.3062</v>
       </c>
       <c r="H8" t="n">
-        <v>0.6427</v>
+        <v>-0.6718</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.5241</v>
+        <v>-0.6344</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9861</v>
+        <v>-1.0813</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2673</v>
+        <v>-0.4477</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2535</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1047</v>
+        <v>-0.2249</v>
       </c>
       <c r="N8" t="n">
-        <v>0.3753</v>
+        <v>-0.2241</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.2706</v>
+        <v>-0.0008</v>
       </c>
       <c r="P8" t="n">
-        <v>0.1953</v>
+        <v>1.5627</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.1721</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1914</v>
+        <v>-0.0159</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4758</v>
+        <v>0.3048</v>
       </c>
       <c r="U8" t="n">
-        <v>0.6672</v>
+        <v>-0.3207</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.0828</v>
+        <v>-0.4365</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6866</v>
+        <v>-2.1353</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6038</v>
+        <v>1.6988</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.3062</v>
+        <v>-0.8814</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6718</v>
+        <v>0.6427</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6344</v>
+        <v>-1.5241</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.0813</v>
+        <v>-0.9861</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.4477</v>
+        <v>0.2673</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.2535</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2249</v>
+        <v>0.1047</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2241</v>
+        <v>0.3753</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0008</v>
+        <v>-0.2706</v>
       </c>
       <c r="P9" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q9" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R9" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.2496</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.1725</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="V9" t="n">
         <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-1.0621</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.6052</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.4568</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.2772</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1495</v>
+        <v>-3.3042</v>
       </c>
       <c r="E10" t="n">
-        <v>1.0938</v>
+        <v>-0.6252</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2433</v>
+        <v>-2.679</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1387</v>
@@ -1234,13 +1234,13 @@
         <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>3.2394</v>
+        <v>1.0847</v>
       </c>
       <c r="T10" t="n">
-        <v>2.7653</v>
+        <v>1.0463</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4742</v>
+        <v>0.0384</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8828</v>
@@ -1267,22 +1267,22 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>11.3832</v>
+        <v>11.6856</v>
       </c>
       <c r="E11" t="n">
-        <v>6.676499999999998</v>
+        <v>6.979200000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>4.7065</v>
+        <v>4.7067</v>
       </c>
       <c r="G11" t="n">
-        <v>7.809800000000001</v>
+        <v>7.809799999999999</v>
       </c>
       <c r="H11" t="n">
         <v>11.1833</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.3735</v>
+        <v>-3.373500000000001</v>
       </c>
       <c r="J11" t="n">
         <v>12.1052</v>
@@ -1303,7 +1303,7 @@
         <v>-1.356</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9769</v>
+        <v>-0.9768999999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-12.6971</v>
@@ -1312,16 +1312,16 @@
         <v>11.7204</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0038</v>
+        <v>1.3064</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8955000000000002</v>
+        <v>1.1979</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1087</v>
+        <v>0.1086000000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>3.5462</v>
+        <v>3.546199999999999</v>
       </c>
       <c r="W11" t="n">
         <v>6.3734</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6145</v>
+        <v>2.2843</v>
       </c>
       <c r="E12" t="n">
-        <v>3.9761</v>
+        <v>2.8638</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.3617</v>
+        <v>-0.5795</v>
       </c>
       <c r="G12" t="n">
         <v>1.136</v>
@@ -1390,13 +1390,13 @@
         <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>1.7752</v>
+        <v>0.4451</v>
       </c>
       <c r="T12" t="n">
-        <v>1.6951</v>
+        <v>0.5828</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0801</v>
+        <v>-0.1377</v>
       </c>
       <c r="V12" t="n">
         <v>-0.6642</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1349</v>
+        <v>1.4867</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1556</v>
+        <v>2.3289</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.0207</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>1.8908</v>
+        <v>2.8452</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9739</v>
+        <v>1.2134</v>
       </c>
       <c r="I13" t="n">
-        <v>0.9169</v>
+        <v>1.6319</v>
       </c>
       <c r="J13" t="n">
-        <v>2.245</v>
+        <v>4.6976</v>
       </c>
       <c r="K13" t="n">
-        <v>1.5976</v>
+        <v>2.6605</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6475</v>
+        <v>2.0371</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.3542</v>
+        <v>-1.8524</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.6237</v>
+        <v>-1.4472</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2694</v>
+        <v>-0.4052</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.586</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.9767</v>
+        <v>-2.1488</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S13" t="n">
-        <v>0.3846</v>
+        <v>-0.1362</v>
       </c>
       <c r="T13" t="n">
-        <v>0.278</v>
+        <v>-0.22</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1066</v>
+        <v>0.0838</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.5545</v>
+        <v>-0.8317</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.1638</v>
+        <v>-0.8317</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8683999999999999</v>
+        <v>1.1386</v>
       </c>
       <c r="E14" t="n">
-        <v>1.52</v>
+        <v>1.3295</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.6516</v>
+        <v>-0.1909</v>
       </c>
       <c r="G14" t="n">
-        <v>2.8452</v>
+        <v>1.2719</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2134</v>
+        <v>0.5838</v>
       </c>
       <c r="I14" t="n">
-        <v>1.6319</v>
+        <v>0.6881</v>
       </c>
       <c r="J14" t="n">
-        <v>4.6976</v>
+        <v>2.5798</v>
       </c>
       <c r="K14" t="n">
-        <v>2.6605</v>
+        <v>2.0261</v>
       </c>
       <c r="L14" t="n">
-        <v>2.0371</v>
+        <v>0.5537</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8524</v>
+        <v>-1.3079</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4472</v>
+        <v>-1.4423</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.4052</v>
+        <v>0.1344</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R14" t="n">
-        <v>1.7581</v>
+        <v>0.9767</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7544</v>
+        <v>-0.1334</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.0289</v>
+        <v>-0.2736</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2744</v>
+        <v>0.1402</v>
       </c>
       <c r="V14" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.8317</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.205</v>
+        <v>0.7421</v>
       </c>
       <c r="E15" t="n">
-        <v>0.7228</v>
+        <v>1.9534</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.5178</v>
+        <v>-1.2113</v>
       </c>
       <c r="G15" t="n">
-        <v>1.2719</v>
+        <v>1.8908</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5838</v>
+        <v>0.9739</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6881</v>
+        <v>0.9169</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5798</v>
+        <v>2.245</v>
       </c>
       <c r="K15" t="n">
-        <v>2.0261</v>
+        <v>1.5976</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5537</v>
+        <v>0.6475</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.3079</v>
+        <v>-0.3542</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.4423</v>
+        <v>-0.6237</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1344</v>
+        <v>0.2694</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R15" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0669</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8803</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1866</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.6093</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-1.1638</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.2129</v>
+        <v>0.3161</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1374</v>
+        <v>1.3397</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.3504</v>
+        <v>-1.0235</v>
       </c>
       <c r="G16" t="n">
         <v>-0.7024</v>
@@ -1702,13 +1702,13 @@
         <v>1.3674</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.2017</v>
+        <v>-0.6726</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2062</v>
+        <v>-0.004</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.9955000000000001</v>
+        <v>-0.6687</v>
       </c>
       <c r="V16" t="n">
         <v>1.4959</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7199</v>
+        <v>-0.1637</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8571</v>
+        <v>2.0593</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.577</v>
+        <v>-2.223</v>
       </c>
       <c r="G17" t="n">
         <v>0.9827</v>
@@ -1780,13 +1780,13 @@
         <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.9882</v>
+        <v>-0.4319</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.341</v>
+        <v>-0.1388</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.6472</v>
+        <v>-0.2931</v>
       </c>
       <c r="V17" t="n">
         <v>-1.4959</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>J. JUAREZ GIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,67 +1813,67 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5422</v>
+        <v>-3.2194</v>
       </c>
       <c r="E18" t="n">
-        <v>-4.7807</v>
+        <v>-3.7654</v>
       </c>
       <c r="F18" t="n">
-        <v>2.2385</v>
+        <v>0.546</v>
       </c>
       <c r="G18" t="n">
-        <v>-6.6609</v>
+        <v>-3.6246</v>
       </c>
       <c r="H18" t="n">
-        <v>-5.4337</v>
+        <v>-2.7614</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2272</v>
+        <v>-0.8632</v>
       </c>
       <c r="J18" t="n">
-        <v>-6.6363</v>
+        <v>-2.6513</v>
       </c>
       <c r="K18" t="n">
-        <v>-4.7354</v>
+        <v>-1.3841</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.9009</v>
+        <v>-1.2673</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.0247</v>
+        <v>-0.9733000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.6984</v>
+        <v>-1.3773</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6737</v>
+        <v>0.4041</v>
       </c>
       <c r="P18" t="n">
-        <v>1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S18" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.4146</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="V18" t="n">
         <v>0</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.5627</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.4425</v>
-      </c>
-      <c r="T18" t="n">
-        <v>2.1876</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.2549</v>
-      </c>
-      <c r="V18" t="n">
-        <v>-0.8865</v>
-      </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5545</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="19">
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-3.6797</v>
+        <v>-4.0181</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9138</v>
+        <v>-2.116</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.7659</v>
+        <v>-1.9021</v>
       </c>
       <c r="G19" t="n">
         <v>-1.1396</v>
@@ -1936,13 +1936,13 @@
         <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>0.1046</v>
+        <v>-0.2338</v>
       </c>
       <c r="T19" t="n">
-        <v>0.2642</v>
+        <v>0.062</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1597</v>
+        <v>-0.2958</v>
       </c>
       <c r="V19" t="n">
         <v>-0.8865</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>C. HOMS LORENZO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9272</v>
+        <v>-4.8876</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.4732</v>
+        <v>-6.4997</v>
       </c>
       <c r="F20" t="n">
-        <v>0.546</v>
+        <v>1.6121</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6246</v>
+        <v>-6.6609</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.7614</v>
+        <v>-5.4337</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.8632</v>
+        <v>-1.2272</v>
       </c>
       <c r="J20" t="n">
-        <v>-2.6513</v>
+        <v>-6.6363</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3841</v>
+        <v>-4.7354</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.2673</v>
+        <v>-1.9009</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.9733000000000001</v>
+        <v>-0.0247</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.3773</v>
+        <v>-0.6984</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4041</v>
+        <v>0.6737</v>
       </c>
       <c r="P20" t="n">
-        <v>0.3907</v>
+        <v>1.5627</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.3674</v>
+        <v>1.5627</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.6933</v>
+        <v>1.0971</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1224</v>
+        <v>0.4686</v>
       </c>
       <c r="U20" t="n">
-        <v>0.4291</v>
+        <v>0.6284999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.8865</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-6.124</v>
+        <v>-5.0622</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.908</v>
+        <v>-4.2002</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.216</v>
+        <v>-0.8619</v>
       </c>
       <c r="G21" t="n">
         <v>-3.809</v>
@@ -2092,13 +2092,13 @@
         <v>1.5627</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.0062</v>
+        <v>-0.9444</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.9546</v>
+        <v>-0.2468</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.0516</v>
+        <v>-0.6976</v>
       </c>
       <c r="V21" t="n">
         <v>0.2772</v>
@@ -2125,28 +2125,28 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.3831</v>
+        <v>-11.3832</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.706700000000001</v>
+        <v>-4.7067</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.6766</v>
+        <v>-6.6763</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.809899999999999</v>
+        <v>-7.8099</v>
       </c>
       <c r="H22" t="n">
         <v>-11.1833</v>
       </c>
       <c r="I22" t="n">
-        <v>3.3735</v>
+        <v>3.373500000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>4.2951</v>
+        <v>4.295100000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>2.938999999999999</v>
+        <v>2.938999999999998</v>
       </c>
       <c r="L22" t="n">
         <v>1.356200000000001</v>
@@ -2173,19 +2173,19 @@
         <v>-1.0038</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1084999999999995</v>
+        <v>-0.1086</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.8955000000000002</v>
+        <v>-0.8953000000000001</v>
       </c>
       <c r="V22" t="n">
-        <v>-3.5462</v>
+        <v>-3.546199999999999</v>
       </c>
       <c r="W22" t="n">
         <v>2.8271</v>
       </c>
       <c r="X22" t="n">
-        <v>-6.373399999999999</v>
+        <v>-6.3734</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484341_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484341_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X22"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,11 +549,16 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>B. MORALES CONILL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +570,78 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.9933</v>
+        <v>4.3679</v>
       </c>
       <c r="E2" t="n">
-        <v>4.7089</v>
+        <v>4.0235</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2844</v>
+        <v>0.3444</v>
       </c>
       <c r="G2" t="n">
-        <v>3.8207</v>
+        <v>2.8641</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4449</v>
+        <v>1.583</v>
       </c>
       <c r="I2" t="n">
-        <v>1.3758</v>
+        <v>1.2811</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1391</v>
+        <v>3.8531</v>
       </c>
       <c r="K2" t="n">
-        <v>3.3576</v>
+        <v>2.0312</v>
       </c>
       <c r="L2" t="n">
-        <v>1.7815</v>
+        <v>1.8219</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.3184</v>
+        <v>-0.989</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9127</v>
+        <v>-0.4482</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.4056</v>
+        <v>-0.5409</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q2" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3674</v>
+        <v>1.9534</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.0145</v>
+        <v>-0.6563</v>
       </c>
       <c r="T2" t="n">
-        <v>0.137</v>
+        <v>-0.3135</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.1515</v>
+        <v>-0.3428</v>
       </c>
       <c r="V2" t="n">
-        <v>1.7731</v>
+        <v>2.16</v>
       </c>
       <c r="W2" t="n">
-        <v>1.3862</v>
+        <v>2.4373</v>
       </c>
       <c r="X2" t="n">
-        <v>0.3869</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>B. MORALES CONILL</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +653,72 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3679</v>
+        <v>3.4654</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0235</v>
+        <v>3.1809</v>
       </c>
       <c r="F3" t="n">
-        <v>0.3444</v>
+        <v>0.2844</v>
       </c>
       <c r="G3" t="n">
-        <v>2.8641</v>
+        <v>2.2928</v>
       </c>
       <c r="H3" t="n">
-        <v>1.583</v>
+        <v>1.524</v>
       </c>
       <c r="I3" t="n">
-        <v>1.2811</v>
+        <v>0.7688</v>
       </c>
       <c r="J3" t="n">
-        <v>3.8531</v>
+        <v>3.6112</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0312</v>
+        <v>2.4367</v>
       </c>
       <c r="L3" t="n">
-        <v>1.8219</v>
+        <v>1.1745</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.989</v>
+        <v>-1.3184</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4482</v>
+        <v>-0.9127</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5409</v>
+        <v>-0.4056</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q3" t="n">
         <v>-1.9534</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9534</v>
+        <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.6563</v>
+        <v>-0.0145</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3135</v>
+        <v>0.137</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3428</v>
+        <v>-0.1515</v>
       </c>
       <c r="V3" t="n">
-        <v>2.16</v>
+        <v>1.7731</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4373</v>
+        <v>1.3862</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.2772</v>
+        <v>0.3869</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0.3321</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,11 +881,16 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. BERMEJO JARAMILLO</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.427</v>
+        <v>1.5279</v>
       </c>
       <c r="E6" t="n">
-        <v>1.2329</v>
+        <v>1.5279</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1942</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0617</v>
+        <v>1.5279</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4257</v>
+        <v>0.921</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.364</v>
+        <v>0.607</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9832</v>
+        <v>1.5279</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6168</v>
+        <v>0.921</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.607</v>
       </c>
       <c r="M6" t="n">
-        <v>1.0786</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8089</v>
+        <v>0</v>
       </c>
       <c r="O6" t="n">
-        <v>0.2696</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3886</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.2497</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1389</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>L. MARTOS RUS</t>
+          <t>P. BERMEJO JARAMILLO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.1051</v>
+        <v>1.427</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3638</v>
+        <v>1.2329</v>
       </c>
       <c r="F7" t="n">
-        <v>1.469</v>
+        <v>0.1942</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2739</v>
+        <v>2.0617</v>
       </c>
       <c r="H7" t="n">
-        <v>0.8294</v>
+        <v>2.4257</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4445</v>
+        <v>-0.364</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7593</v>
+        <v>0.9832</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7188</v>
+        <v>1.6168</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0405</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5145999999999999</v>
+        <v>1.0786</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1105</v>
+        <v>0.8089</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4041</v>
+        <v>0.2696</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.3907</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1671</v>
+        <v>0.3886</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.1464</v>
+        <v>0.2497</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3135</v>
+        <v>0.1389</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0549</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>L. MARTOS RUS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0366</v>
+        <v>1.1051</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7765</v>
+        <v>-0.3638</v>
       </c>
       <c r="F8" t="n">
-        <v>0.74</v>
+        <v>1.469</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.3062</v>
+        <v>1.2739</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.6718</v>
+        <v>0.8294</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6344</v>
+        <v>0.4445</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.0813</v>
+        <v>0.7593</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.4477</v>
+        <v>0.7188</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6336000000000001</v>
+        <v>0.0405</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2249</v>
+        <v>0.5145999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2241</v>
+        <v>0.1105</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0008</v>
+        <v>0.4041</v>
       </c>
       <c r="P8" t="n">
-        <v>1.5627</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0159</v>
+        <v>0.1671</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3048</v>
+        <v>-0.1464</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3207</v>
+        <v>0.3135</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.2772</v>
+        <v>0.0549</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>M. FENÉS HERNÁNDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,58 +1151,58 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4365</v>
+        <v>0.614</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1353</v>
+        <v>0.614</v>
       </c>
       <c r="F9" t="n">
-        <v>1.6988</v>
+        <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8814</v>
+        <v>0.614</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6427</v>
+        <v>0.614</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5241</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9861</v>
+        <v>0.614</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2673</v>
+        <v>0.614</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2535</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1047</v>
+        <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>0.3753</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2706</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2496</v>
+        <v>0</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1725</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>0.4221</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1172,12 +1212,17 @@
       </c>
       <c r="X9" t="n">
         <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3042</v>
+        <v>-0.4365</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6252</v>
+        <v>-2.1353</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.679</v>
+        <v>1.6988</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.1387</v>
+        <v>-0.8814</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.3152</v>
+        <v>0.6427</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.8235</v>
+        <v>-1.5241</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3135</v>
+        <v>-0.9861</v>
       </c>
       <c r="K10" t="n">
-        <v>1.1921</v>
+        <v>0.2673</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1214</v>
+        <v>-1.2535</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.4522</v>
+        <v>0.1047</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.5073</v>
+        <v>0.3753</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.9449</v>
+        <v>-0.2706</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3674</v>
+        <v>0.1953</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>1.1721</v>
       </c>
       <c r="S10" t="n">
-        <v>1.0847</v>
+        <v>0.2496</v>
       </c>
       <c r="T10" t="n">
-        <v>1.0463</v>
+        <v>-0.1725</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0384</v>
+        <v>0.4221</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8828</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.0549</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,229 +1317,240 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>11.6856</v>
+        <v>-0.6505</v>
       </c>
       <c r="E11" t="n">
-        <v>6.979200000000001</v>
+        <v>-1.3905</v>
       </c>
       <c r="F11" t="n">
-        <v>4.7067</v>
+        <v>0.74</v>
       </c>
       <c r="G11" t="n">
-        <v>7.809799999999999</v>
+        <v>-1.9202</v>
       </c>
       <c r="H11" t="n">
-        <v>11.1833</v>
+        <v>-1.2858</v>
       </c>
       <c r="I11" t="n">
-        <v>-3.373500000000001</v>
+        <v>-0.6344</v>
       </c>
       <c r="J11" t="n">
-        <v>12.1052</v>
+        <v>-1.6953</v>
       </c>
       <c r="K11" t="n">
-        <v>14.1224</v>
+        <v>-1.0617</v>
       </c>
       <c r="L11" t="n">
-        <v>-2.0173</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-4.295199999999999</v>
+        <v>-0.2249</v>
       </c>
       <c r="N11" t="n">
-        <v>-2.9392</v>
+        <v>-0.2241</v>
       </c>
       <c r="O11" t="n">
-        <v>-1.356</v>
+        <v>-0.0008</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9768999999999999</v>
+        <v>1.5627</v>
       </c>
       <c r="Q11" t="n">
-        <v>-12.6971</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>11.7204</v>
+        <v>1.5627</v>
       </c>
       <c r="S11" t="n">
-        <v>1.3064</v>
+        <v>-0.0159</v>
       </c>
       <c r="T11" t="n">
-        <v>1.1979</v>
+        <v>0.3048</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1086000000000001</v>
+        <v>-0.3207</v>
       </c>
       <c r="V11" t="n">
-        <v>3.546199999999999</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>6.3734</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.827</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. MURCIANO PUJADAS</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.2843</v>
+        <v>-3.3042</v>
       </c>
       <c r="E12" t="n">
-        <v>2.8638</v>
+        <v>-0.6252</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.5795</v>
+        <v>-2.679</v>
       </c>
       <c r="G12" t="n">
-        <v>1.136</v>
+        <v>-1.1387</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0156</v>
+        <v>-0.3152</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1204</v>
+        <v>-0.8235</v>
       </c>
       <c r="J12" t="n">
-        <v>2.8633</v>
+        <v>1.3135</v>
       </c>
       <c r="K12" t="n">
-        <v>1.7421</v>
+        <v>1.1921</v>
       </c>
       <c r="L12" t="n">
-        <v>1.1212</v>
+        <v>0.1214</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.7273</v>
+        <v>-2.4522</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.7265</v>
+        <v>-1.5073</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0008</v>
+        <v>-0.9449</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3674</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1953</v>
+        <v>-2.9301</v>
       </c>
       <c r="R12" t="n">
         <v>1.5627</v>
       </c>
       <c r="S12" t="n">
-        <v>0.4451</v>
+        <v>1.0847</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5828</v>
+        <v>1.0463</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1377</v>
+        <v>0.0384</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.6642</v>
+        <v>-1.8828</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3869</v>
+        <v>-0.0549</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.2772</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>I. MASPONS MOLINS</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>C.B. GRANOLLERS</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4867</v>
+        <v>11.6857</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3289</v>
+        <v>6.979099999999997</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.8421999999999999</v>
+        <v>4.706700000000001</v>
       </c>
       <c r="G13" t="n">
-        <v>2.8452</v>
+        <v>7.809800000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.2134</v>
+        <v>11.1834</v>
       </c>
       <c r="I13" t="n">
-        <v>1.6319</v>
+        <v>-3.3735</v>
       </c>
       <c r="J13" t="n">
-        <v>4.6976</v>
+        <v>12.1052</v>
       </c>
       <c r="K13" t="n">
-        <v>2.6605</v>
+        <v>14.1225</v>
       </c>
       <c r="L13" t="n">
-        <v>2.0371</v>
+        <v>-2.0173</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.8524</v>
+        <v>-4.295199999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.4472</v>
+        <v>-2.9392</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.4052</v>
+        <v>-1.356</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.3907</v>
+        <v>-0.9768999999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-2.1488</v>
+        <v>-12.6971</v>
       </c>
       <c r="R13" t="n">
-        <v>1.7581</v>
+        <v>11.7204</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.1362</v>
+        <v>1.3064</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.22</v>
+        <v>1.1979</v>
       </c>
       <c r="U13" t="n">
-        <v>0.0838</v>
+        <v>0.1086</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.8317</v>
+        <v>3.546199999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>6.3734</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.8317</v>
-      </c>
+        <v>-2.827</v>
+      </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MARTÍN ADELANTADO</t>
+          <t>A. MURCIANO PUJADAS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1562,78 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.1386</v>
+        <v>2.2843</v>
       </c>
       <c r="E14" t="n">
-        <v>1.3295</v>
+        <v>2.8638</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1909</v>
+        <v>-0.5795</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2719</v>
+        <v>1.136</v>
       </c>
       <c r="H14" t="n">
-        <v>0.5838</v>
+        <v>0.0156</v>
       </c>
       <c r="I14" t="n">
-        <v>0.6881</v>
+        <v>1.1204</v>
       </c>
       <c r="J14" t="n">
-        <v>2.5798</v>
+        <v>2.8633</v>
       </c>
       <c r="K14" t="n">
-        <v>2.0261</v>
+        <v>1.7421</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5537</v>
+        <v>1.1212</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.3079</v>
+        <v>-1.7273</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.4423</v>
+        <v>-1.7265</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1344</v>
+        <v>-0.0008</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.3674</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9767</v>
+        <v>-0.1953</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9767</v>
+        <v>1.5627</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1334</v>
+        <v>0.4451</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2736</v>
+        <v>0.5828</v>
       </c>
       <c r="U14" t="n">
-        <v>0.1402</v>
+        <v>-0.1377</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.3869</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SALMERON SEGU</t>
+          <t>A. MARTÍN ADELANTADO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.7421</v>
+        <v>1.5279</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9534</v>
+        <v>1.5279</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.2113</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8908</v>
+        <v>1.5279</v>
       </c>
       <c r="H15" t="n">
-        <v>0.9739</v>
+        <v>0.921</v>
       </c>
       <c r="I15" t="n">
-        <v>0.9169</v>
+        <v>0.607</v>
       </c>
       <c r="J15" t="n">
-        <v>2.245</v>
+        <v>1.5279</v>
       </c>
       <c r="K15" t="n">
-        <v>1.5976</v>
+        <v>0.921</v>
       </c>
       <c r="L15" t="n">
-        <v>0.6475</v>
+        <v>0.607</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.3542</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.6237</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>0.2694</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.008200000000000001</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.07580000000000001</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.08400000000000001</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>0.6093</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.1638</v>
+        <v>0</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>O. HERAS FLECHA</t>
+          <t>I. MASPONS MOLINS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3161</v>
+        <v>1.4867</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3397</v>
+        <v>2.3289</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.0235</v>
+        <v>-0.8421999999999999</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.7024</v>
+        <v>2.8452</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6357</v>
+        <v>1.2134</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.0667</v>
+        <v>1.6319</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0198</v>
+        <v>4.6976</v>
       </c>
       <c r="K16" t="n">
-        <v>1.086</v>
+        <v>2.6605</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.06610000000000001</v>
+        <v>2.0371</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7223</v>
+        <v>-1.8524</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.7217</v>
+        <v>-1.4472</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.4052</v>
       </c>
       <c r="P16" t="n">
-        <v>0.1953</v>
+        <v>-0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.1721</v>
+        <v>-2.1488</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3674</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6726</v>
+        <v>-0.1362</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.004</v>
+        <v>-0.22</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6687</v>
+        <v>0.0838</v>
       </c>
       <c r="V16" t="n">
-        <v>1.4959</v>
+        <v>-0.8317</v>
       </c>
       <c r="W16" t="n">
-        <v>1.4959</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.8317</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. TORNÉ DELAURENS</t>
+          <t>A. VIÑALLONGA GOMEZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1637</v>
+        <v>0.914</v>
       </c>
       <c r="E17" t="n">
-        <v>2.0593</v>
+        <v>0.914</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.223</v>
+        <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9827</v>
+        <v>0.914</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.4057</v>
+        <v>0.307</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3885</v>
+        <v>0.607</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9562</v>
+        <v>0.914</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1064</v>
+        <v>0.307</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8498</v>
+        <v>0.607</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.9735</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5121</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5387</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4319</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1388</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2931</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.4959</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JUAREZ GIMENEZ</t>
+          <t>M. TORNÉ DELAURENS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-3.2194</v>
+        <v>0.914</v>
       </c>
       <c r="E18" t="n">
-        <v>-3.7654</v>
+        <v>0.914</v>
       </c>
       <c r="F18" t="n">
-        <v>0.546</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>-3.6246</v>
+        <v>0.914</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7614</v>
+        <v>0.307</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8632</v>
+        <v>0.607</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.6513</v>
+        <v>0.914</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.3841</v>
+        <v>0.307</v>
       </c>
       <c r="L18" t="n">
-        <v>-1.2673</v>
+        <v>0.607</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.9733000000000001</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.3773</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4041</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3907</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.3674</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0145</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.4146</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>0.4291</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. TOURE JABBY</t>
+          <t>M. SALMERON SEGU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.0181</v>
+        <v>0.7421</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.116</v>
+        <v>1.9534</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9021</v>
+        <v>-1.2113</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1396</v>
+        <v>1.8908</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.9622</v>
+        <v>0.9739</v>
       </c>
       <c r="I19" t="n">
-        <v>0.8225</v>
+        <v>0.9169</v>
       </c>
       <c r="J19" t="n">
-        <v>0.3029</v>
+        <v>2.245</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.385</v>
+        <v>1.5976</v>
       </c>
       <c r="L19" t="n">
-        <v>0.6879</v>
+        <v>0.6475</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.4425</v>
+        <v>-0.3542</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.5771</v>
+        <v>-0.6237</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1346</v>
+        <v>0.2694</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.7581</v>
+        <v>-0.586</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
         <v>0.3907</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2338</v>
+        <v>-0.008200000000000001</v>
       </c>
       <c r="T19" t="n">
-        <v>0.062</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2958</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8865</v>
+        <v>-0.5545</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3321</v>
+        <v>0.6093</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5545</v>
+        <v>-1.1638</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>C. HOMS LORENZO</t>
+          <t>O. HERAS FLECHA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.8876</v>
+        <v>0.3161</v>
       </c>
       <c r="E20" t="n">
-        <v>-6.4997</v>
+        <v>1.3397</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6121</v>
+        <v>-1.0235</v>
       </c>
       <c r="G20" t="n">
-        <v>-6.6609</v>
+        <v>-0.7024</v>
       </c>
       <c r="H20" t="n">
-        <v>-5.4337</v>
+        <v>-0.6357</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.2272</v>
+        <v>-0.0667</v>
       </c>
       <c r="J20" t="n">
-        <v>-6.6363</v>
+        <v>1.0198</v>
       </c>
       <c r="K20" t="n">
-        <v>-4.7354</v>
+        <v>1.086</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.9009</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0247</v>
+        <v>-1.7223</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.6984</v>
+        <v>-1.7217</v>
       </c>
       <c r="O20" t="n">
-        <v>0.6737</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P20" t="n">
-        <v>1.5627</v>
+        <v>0.1953</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R20" t="n">
-        <v>1.5627</v>
+        <v>1.3674</v>
       </c>
       <c r="S20" t="n">
-        <v>1.0971</v>
+        <v>-0.6726</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4686</v>
+        <v>-0.004</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6284999999999999</v>
+        <v>-0.6687</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.8865</v>
+        <v>1.4959</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3321</v>
+        <v>1.4959</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. VIÑALLONGA GOMEZ</t>
+          <t>A. MARTIN ADELANTADO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.0622</v>
+        <v>-0.3894</v>
       </c>
       <c r="E21" t="n">
-        <v>-4.2002</v>
+        <v>-0.1985</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8619</v>
+        <v>-0.1909</v>
       </c>
       <c r="G21" t="n">
-        <v>-3.809</v>
+        <v>-0.256</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.7713</v>
+        <v>-0.3372</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0377</v>
+        <v>0.08110000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.0819</v>
+        <v>1.0519</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7752</v>
+        <v>1.1051</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3067</v>
+        <v>-0.0533</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.7271</v>
+        <v>-1.3079</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.9962</v>
+        <v>-1.4423</v>
       </c>
       <c r="O21" t="n">
-        <v>0.269</v>
+        <v>0.1344</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.1488</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9444</v>
+        <v>-0.1334</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2468</v>
+        <v>-0.2736</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6976</v>
+        <v>0.1402</v>
       </c>
       <c r="V21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>M. TORNE DELAURENS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,68 +2226,484 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-11.3832</v>
+        <v>-1.0776</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.7067</v>
+        <v>1.1454</v>
       </c>
       <c r="F22" t="n">
-        <v>-6.6763</v>
+        <v>-2.223</v>
       </c>
       <c r="G22" t="n">
-        <v>-7.8099</v>
+        <v>0.0688</v>
       </c>
       <c r="H22" t="n">
+        <v>-0.7127</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.7815</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1.0422</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0.7994</v>
+      </c>
+      <c r="L22" t="n">
+        <v>0.2428</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-0.9735</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-1.5121</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0.5387</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0.7814</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1.7581</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.4319</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.1388</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.2931</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.4959</v>
+      </c>
+      <c r="W22" t="n">
+        <v>1.2186</v>
+      </c>
+      <c r="X22" t="n">
+        <v>-2.7145</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>J. JUAREZ GIMENEZ</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>1</v>
+      </c>
+      <c r="D23" t="n">
+        <v>-3.2194</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-3.7654</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.546</v>
+      </c>
+      <c r="G23" t="n">
+        <v>-3.6246</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-2.7614</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.8632</v>
+      </c>
+      <c r="J23" t="n">
+        <v>-2.6513</v>
+      </c>
+      <c r="K23" t="n">
+        <v>-1.3841</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-1.2673</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-0.9733000000000001</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-1.3773</v>
+      </c>
+      <c r="O23" t="n">
+        <v>0.4041</v>
+      </c>
+      <c r="P23" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R23" t="n">
+        <v>1.3674</v>
+      </c>
+      <c r="S23" t="n">
+        <v>0.0145</v>
+      </c>
+      <c r="T23" t="n">
+        <v>-0.4146</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="V23" t="n">
+        <v>0</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X23" t="n">
+        <v>-0.2772</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>O. TOURE JABBY</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" t="n">
+        <v>-4.0181</v>
+      </c>
+      <c r="E24" t="n">
+        <v>-2.116</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-1.9021</v>
+      </c>
+      <c r="G24" t="n">
+        <v>-1.1396</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-1.9622</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.8225</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-0.385</v>
+      </c>
+      <c r="L24" t="n">
+        <v>0.6879</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-1.4425</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-1.5771</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.1346</v>
+      </c>
+      <c r="P24" t="n">
+        <v>-1.7581</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.2338</v>
+      </c>
+      <c r="T24" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.2958</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="W24" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>C. HOMS LORENZO</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-4.8876</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-6.4997</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.6121</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-6.6609</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-5.4337</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.2272</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-6.6363</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-4.7354</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-1.9009</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.0247</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.6984</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.6737</v>
+      </c>
+      <c r="P25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S25" t="n">
+        <v>1.0971</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0.6284999999999999</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="W25" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.5545</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A. VINALLONGA GOMEZ</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-5.9761</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-5.1142</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.8619</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.723</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-3.0783</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-1.6447</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.9959</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-1.0821</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-1.9137</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.7271</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.9962</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.586</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.5627</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.9444</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.2468</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.6976</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484341_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>C.B. GRANOLLERS</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>-11.3831</v>
+      </c>
+      <c r="E27" t="n">
+        <v>-4.706699999999999</v>
+      </c>
+      <c r="F27" t="n">
+        <v>-6.676299999999999</v>
+      </c>
+      <c r="G27" t="n">
+        <v>-7.809799999999999</v>
+      </c>
+      <c r="H27" t="n">
         <v>-11.1833</v>
       </c>
-      <c r="I22" t="n">
-        <v>3.373500000000001</v>
-      </c>
-      <c r="J22" t="n">
+      <c r="I27" t="n">
+        <v>3.3735</v>
+      </c>
+      <c r="J27" t="n">
         <v>4.295100000000001</v>
       </c>
-      <c r="K22" t="n">
-        <v>2.938999999999998</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K27" t="n">
+        <v>2.939099999999998</v>
+      </c>
+      <c r="L27" t="n">
         <v>1.356200000000001</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M27" t="n">
         <v>-12.1052</v>
       </c>
-      <c r="N22" t="n">
+      <c r="N27" t="n">
         <v>-14.1225</v>
       </c>
-      <c r="O22" t="n">
+      <c r="O27" t="n">
         <v>2.0173</v>
       </c>
-      <c r="P22" t="n">
+      <c r="P27" t="n">
         <v>0.9767</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="Q27" t="n">
         <v>-11.7206</v>
       </c>
-      <c r="R22" t="n">
+      <c r="R27" t="n">
         <v>12.6972</v>
       </c>
-      <c r="S22" t="n">
+      <c r="S27" t="n">
         <v>-1.0038</v>
       </c>
-      <c r="T22" t="n">
+      <c r="T27" t="n">
         <v>-0.1086</v>
       </c>
-      <c r="U22" t="n">
+      <c r="U27" t="n">
         <v>-0.8953000000000001</v>
       </c>
-      <c r="V22" t="n">
+      <c r="V27" t="n">
         <v>-3.546199999999999</v>
       </c>
-      <c r="W22" t="n">
+      <c r="W27" t="n">
         <v>2.8271</v>
       </c>
-      <c r="X22" t="n">
-        <v>-6.3734</v>
-      </c>
+      <c r="X27" t="n">
+        <v>-6.373399999999999</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
